--- a/code/api-autotest-tool/src/case/case.xlsx
+++ b/code/api-autotest-tool/src/case/case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2087\Desktop\REPO\pw-z.github.io\code\api-autotest-tool\src\case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4FE570-F897-4DEF-8916-A2034776438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287F2067-0809-480D-B970-4C0013873DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+  <si>
+    <t>CaseID</t>
+  </si>
   <si>
     <t>CaseName</t>
   </si>
@@ -85,52 +88,27 @@
     <t>application/x-www-form-urlencoded;charset=UTF-8</t>
   </si>
   <si>
+    <t>"TYPE_DESC":"机构类型"
+"TEXT":"公共模块"</t>
+  </si>
+  <si>
     <t>token</t>
   </si>
   <si>
+    <t>SELECT * FROM BASE_PARAM</t>
+  </si>
+  <si>
+    <t>COUNT(*):32
+count(*):31</t>
+  </si>
+  <si>
+    <t>登录获取token2</t>
+  </si>
+  <si>
     <t>SELECT count(*) FROM BASE_PARAM</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>登录获取token2</t>
-  </si>
-  <si>
-    <t>登录获取token3</t>
-  </si>
-  <si>
-    <t>参数获取2</t>
-  </si>
-  <si>
-    <t>参数获取3</t>
-  </si>
-  <si>
-    <t>参数获取4</t>
-  </si>
-  <si>
-    <t>信息获取1</t>
-  </si>
-  <si>
-    <t>获取【小小测试001】客户信息1</t>
-  </si>
-  <si>
-    <t>/irs</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>"CUST_TRADECODE":"2087001"</t>
-  </si>
-  <si>
-    <t>信息获取2</t>
-  </si>
-  <si>
-    <t>获取【小小测试001】客户信息2</t>
-  </si>
-  <si>
-    <t>ID</t>
+    <t>count(*):32</t>
   </si>
 </sst>
 </file>
@@ -228,7 +206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -262,13 +240,10 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="3" customWidth="1"/>
@@ -599,587 +574,133 @@
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="28.8">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="6">
         <v>111</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="8"/>
       <c r="I2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="7"/>
-      <c r="M2" s="6"/>
+      <c r="M2" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="28.8">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="6">
         <v>111</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="8"/>
       <c r="I3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="6">
-        <v>111</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="6">
-        <v>111</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="6">
-        <v>111</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="6">
-        <v>111</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A8" s="9">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="6">
-        <v>111</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A9" s="9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="6">
-        <v>111</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="6">
-        <v>111</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A11" s="9">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="P3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="6">
-        <v>111</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A12" s="9">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="6">
-        <v>111</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="2" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A13" s="9">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="6">
-        <v>111</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="22.05" customHeight="1">
-      <c r="A14" s="9">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6">
-        <v>110</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="12"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.05" customHeight="1">
-      <c r="A15" s="9">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="6">
-        <v>110</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/code/api-autotest-tool/src/case/case.xlsx
+++ b/code/api-autotest-tool/src/case/case.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2087\Desktop\REPO\pw-z.github.io\code\api-autotest-tool\src\case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287F2067-0809-480D-B970-4C0013873DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A78E9CB-02C4-4505-9BB9-9150B163654D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" tabRatio="780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="9" r:id="rId1"/>
+    <sheet name="clear" sheetId="10" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="171">
   <si>
     <t>CaseID</t>
   </si>
@@ -79,6 +80,9 @@
     <t>post</t>
   </si>
   <si>
+    <t>http://10.243.141.100</t>
+  </si>
+  <si>
     <t>/secu</t>
   </si>
   <si>
@@ -86,6 +90,13 @@
   </si>
   <si>
     <t>application/x-www-form-urlencoded;charset=UTF-8</t>
+  </si>
+  <si>
+    <t>data={
+    "userId":"143374",
+    "PASSWORD":"qwer1234",
+    "f":"SECU_Login"
+}</t>
   </si>
   <si>
     <t>"TYPE_DESC":"机构类型"
@@ -109,6 +120,1038 @@
   </si>
   <si>
     <t>count(*):32</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>delayTime</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>参数获取</t>
+  </si>
+  <si>
+    <t>登录获取token</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>获取系统交易日期</t>
+  </si>
+  <si>
+    <t>/irs</t>
+  </si>
+  <si>
+    <t>data={
+    "f":"IRS_CLEAR_QY_DATE",
+    "u":"143374",
+    "l":"${token}",
+    "e":"999"
+}</t>
+  </si>
+  <si>
+    <t>TRADE_DATE</t>
+  </si>
+  <si>
+    <t>获取【小小测试001】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试001",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>"total":1</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_01
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_01
+ACCOUNT_NO:ACC_NO_01
+CUSTOMER_ID:CUSTOMER_ID_01
+MARGIN_NO:MARGIN_NO_01</t>
+  </si>
+  <si>
+    <t>获取【小小测试002】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试002",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_02
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_02
+ACCOUNT_NO:ACC_NO_02
+CUSTOMER_ID:CUSTOMER_ID_02
+MARGIN_NO:MARGIN_NO_02</t>
+  </si>
+  <si>
+    <t>获取【小小测试003】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试003",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_03
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_03
+ACCOUNT_NO:ACC_NO_03
+CUSTOMER_ID:CUSTOMER_ID_03
+MARGIN_NO:MARGIN_NO_03</t>
+  </si>
+  <si>
+    <t>获取【小小测试004】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试004",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_04
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_04
+ACCOUNT_NO:ACC_NO_04
+CUSTOMER_ID:CUSTOMER_ID_04
+MARGIN_NO:MARGIN_NO_04</t>
+  </si>
+  <si>
+    <t>获取【小小测试005】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试005",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_05
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_05
+ACCOUNT_NO:ACC_NO_05
+CUSTOMER_ID:CUSTOMER_ID_05
+MARGIN_NO:MARGIN_NO_05</t>
+  </si>
+  <si>
+    <t>获取【小小测试006】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试006",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_06
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_06
+ACCOUNT_NO:ACC_NO_06
+CUSTOMER_ID:CUSTOMER_ID_06
+MARGIN_NO:MARGIN_NO_06</t>
+  </si>
+  <si>
+    <t>获取【小小测试007】客户信息</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "CUSTOMER_ID": "",
+    "ACCOUNT_NO": "",
+    "MARGIN_NO": "",
+    "CUSTOMER_NAME_CH": "小小测试007",
+    "SIGN_STATUS": "*",
+    "CUSTOMER_STATUS": "*",
+    "MARGIN_STATUS": "*",
+    "LOCALSYS_ID": "",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID:LOCALSYS_ID_07
+CUSTOMER_NAME_CH:CUSTOMER_NAME_CH_07
+ACCOUNT_NO:ACC_NO_07
+CUSTOMER_ID:CUSTOMER_ID_07
+MARGIN_NO:MARGIN_NO_07</t>
+  </si>
+  <si>
+    <t>测试环境检测（本条用例不通过，后续步骤无意义）</t>
+  </si>
+  <si>
+    <t>交易日期=20210319&amp;&amp;系统日期=20210320</t>
+  </si>
+  <si>
+    <t>"TRADE_DATE":"20210319"
+"SYS_DATE":"20210320"</t>
+  </si>
+  <si>
+    <t>保证金要求明细表为空（DE07）</t>
+  </si>
+  <si>
+    <t>select COUNT(*) from DAYEND_MARGING_REQINFO</t>
+  </si>
+  <si>
+    <t>COUNT(*):0</t>
+  </si>
+  <si>
+    <t>当日接单情况明细表为空（DE01）</t>
+  </si>
+  <si>
+    <t>select COUNT(*) from DAYEND_DAILY_ORDERS_INFO</t>
+  </si>
+  <si>
+    <t>次日待结算资金清单表为空(DE03)</t>
+  </si>
+  <si>
+    <t>select COUNT(*) from DAYEND_FEE_SETTLEMENT_INFO</t>
+  </si>
+  <si>
+    <t>季度的总计值表为空(DE17)</t>
+  </si>
+  <si>
+    <t>select COUNT(*) from DAYEND_FEE_TOTAL</t>
+  </si>
+  <si>
+    <t>费用结算的明细清单表为空(DE18)</t>
+  </si>
+  <si>
+    <t>select COUNT(*) from DAYEND_FEE_Settlement_INFO</t>
+  </si>
+  <si>
+    <t>利息积数表为空</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM INTEREST_ACCRUAL</t>
+  </si>
+  <si>
+    <t>利息报表结果表为空</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM INTEREST_REPORT</t>
+  </si>
+  <si>
+    <t>SCH利息总额表为空</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM INTEREST_SCHC</t>
+  </si>
+  <si>
+    <t>结息表为空</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM INTEREST_SETTLEMENT</t>
+  </si>
+  <si>
+    <t>清算步骤表为初始状态</t>
+  </si>
+  <si>
+    <t>SELECT SUM(CLEAR_RESULT) FROM CLEARING_PROCEDURE</t>
+  </si>
+  <si>
+    <t>SUM(CLEAR_RESULT):0</t>
+  </si>
+  <si>
+    <t>费率表环境校验</t>
+  </si>
+  <si>
+    <t>手续费费率表BASE_FEE_RATE仅有一条通用费率</t>
+  </si>
+  <si>
+    <t>data={
+    "ACCOUNT_NO": "",
+    "CUSTOMER_ID": "",
+    "MARGIN_NO": "",
+    "PRODUCT": "IRS",
+    "CUSTOMER_NAME_CH": "",
+    "LOCALSYS_ID": "",
+    "page_count": 10,
+    "page_NO": 1,
+    "tableDataID": "GETDATA_IRS_CustomerFeeRate",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>"total":1
+"LOCALSYS_ID":"$"</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM BASE_FEE_RATE t</t>
+  </si>
+  <si>
+    <t>COUNT(*):1</t>
+  </si>
+  <si>
+    <t>保证金率表BASE_MARGIN_RATE仅有一条通用数据</t>
+  </si>
+  <si>
+    <t>data={
+    "ACCOUNT_NO": "",
+    "CUSTOMER_ID": "",
+    "MARGIN_NO": "",
+    "PRODUCT": "IRS",
+    "CUSTOMER_NAME_CH": "",
+    "LOCALSYS_ID": "",
+    "page_count": 10,
+    "page_NO": 1,
+    "tableDataID": "GETDATA_IRS_CustomerMarginRate",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM BASE_MARGIN_RATE t</t>
+  </si>
+  <si>
+    <t>利率表BASE_INTEREST_RATE仅有一条20210101数据</t>
+  </si>
+  <si>
+    <t>data={
+    "EFFECT_DATE": null,
+    "PRODUCT": "IRS",
+    "serachmodel": "0",
+    "page_count": 10,
+    "page_NO": 1,
+    "EFFECT_DATE1": "20210319",
+    "EFFECT_DATE2": "20210320",
+    "tableDataID": "GETDATA_IRS_CUSTOMERRATE",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>"total":1
+"EFFECT_DATE":"20210101"
+"MINMARGIN_AIR":"1"
+"CHANGEMARGIN_AIR":"1"</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM BASE_INTEREST_RATE t</t>
+  </si>
+  <si>
+    <t>冒烟测试</t>
+  </si>
+  <si>
+    <t>获取清算文件</t>
+  </si>
+  <si>
+    <t>cd ~/share/sftp/today
+rm *
+echo "push 20210319DE07.xml"
+echo '&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;file&gt;
+ &lt;head&gt;
+  &lt;memid&gt;0000144&lt;/memid&gt;
+  &lt;filetype&gt;DE07&lt;/filetype&gt;
+  &lt;filename&gt;20210319DE07.xml&lt;/filename&gt;
+  &lt;recordnum&gt;7&lt;/recordnum&gt;
+ &lt;/head&gt;
+ &lt;body&gt;
+  &lt;rows&gt;
+   &lt;row id="1"&gt;
+    &lt;entityid&gt;2087001&lt;/entityid&gt;
+    &lt;lowmargin&gt;10000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;10000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+   &lt;row id="2"&gt;
+    &lt;entityid&gt;2087002&lt;/entityid&gt;
+    &lt;lowmargin&gt;10000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;10000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+   &lt;row id="3"&gt;
+    &lt;entityid&gt;2087003&lt;/entityid&gt;
+    &lt;lowmargin&gt;10000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;10000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+   &lt;row id="4"&gt;
+    &lt;entityid&gt;2087004&lt;/entityid&gt;
+    &lt;lowmargin&gt;10000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;10000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+   &lt;row id="5"&gt;
+    &lt;entityid&gt;2087005&lt;/entityid&gt;
+    &lt;lowmargin&gt;10000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;10000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+   &lt;row id="6"&gt;
+    &lt;entityid&gt;2087006&lt;/entityid&gt;
+    &lt;lowmargin&gt;10000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;10000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+   &lt;row id="7"&gt;
+    &lt;entityid&gt;2087007&lt;/entityid&gt;
+    &lt;lowmargin&gt;120000.00&lt;/lowmargin&gt;
+    &lt;exceedmargin&gt;0.00&lt;/exceedmargin&gt;
+    &lt;specialmargin&gt;0.00&lt;/specialmargin&gt;
+    &lt;totalmargin&gt;120000.00&lt;/totalmargin&gt;
+    &lt;cashratio&gt;1.0&lt;/cashratio&gt;
+    &lt;marginbalance1&gt;0.00&lt;/marginbalance1&gt;
+    &lt;marginbalance2&gt;10000.00&lt;/marginbalance2&gt;
+   &lt;/row&gt;
+  &lt;/rows&gt;
+ &lt;/body&gt;
+&lt;/file&gt;' &gt; 20210319DE07.xml
+cat 20210319DE07.xml
+echo "push empty 20210319DE01.xml"
+echo '&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;file&gt;
+ &lt;head&gt;
+  &lt;memid&gt;0000144&lt;/memid&gt;
+  &lt;filetype&gt;DE01&lt;/filetype&gt;
+  &lt;filename&gt;20210319DE01.xml&lt;/filename&gt;
+  &lt;recordnum&gt;0&lt;/recordnum&gt;
+ &lt;/head&gt;
+ &lt;body&gt;
+  &lt;rows&gt;
+  &lt;/rows&gt;
+ &lt;/body&gt;
+&lt;/file&gt;' &gt; 20210319DE01.xml
+echo "push empty 20210319DE03.xml"
+echo '&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;file&gt;
+ &lt;head&gt;
+  &lt;memid&gt;0000144&lt;/memid&gt;
+  &lt;filetype&gt;DE03&lt;/filetype&gt;
+  &lt;filename&gt;20210319DE03.xml&lt;/filename&gt;
+  &lt;recordnum&gt;0&lt;/recordnum&gt;
+ &lt;/head&gt;
+ &lt;body&gt;
+  &lt;rows&gt;
+  &lt;/rows&gt;
+ &lt;/body&gt;
+&lt;/file&gt;' &gt; 20210319DE03.xml
+echo "push empty 20210319DE17.xml"
+echo '&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;file&gt;
+ &lt;head&gt;
+  &lt;memid&gt;0000144&lt;/memid&gt;
+  &lt;filetype&gt;DE17&lt;/filetype&gt;
+  &lt;filename&gt;20210319DE17.xml&lt;/filename&gt;
+  &lt;recordnum&gt;0&lt;/recordnum&gt;
+ &lt;/head&gt;
+ &lt;body&gt;
+  &lt;rows&gt;
+  &lt;/rows&gt;
+ &lt;/body&gt;
+&lt;/file&gt;' &gt; 20210319DE17.xml
+echo "push empty 20210319DE18.xml"
+echo '&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;file&gt;
+ &lt;head&gt;
+  &lt;memid&gt;0000144&lt;/memid&gt;
+  &lt;filetype&gt;DE18&lt;/filetype&gt;
+  &lt;filename&gt;20210319DE18.xml&lt;/filename&gt;
+  &lt;recordnum&gt;0&lt;/recordnum&gt;
+ &lt;/head&gt;
+ &lt;body&gt;
+  &lt;rows&gt;
+  &lt;/rows&gt;
+ &lt;/body&gt;
+&lt;/file&gt;' &gt; 20210319DE18.xml</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_GETSCHDATA",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>select * from CLEARING_PROCEDURE where TRADE_DATE = 20210319 and CLEAR_STEP = 'IMPORT_FILE'</t>
+  </si>
+  <si>
+    <t>CLEAR_RESULT:1</t>
+  </si>
+  <si>
+    <t>参数完整清算成功</t>
+  </si>
+  <si>
+    <t>data={
+    "PREPARE_FLAG": "0",
+    "f": "IRS_START_CLEAR",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>select * from CLEARING_PROCEDURE where TRADE_DATE = 20210319 and CLEAR_STEP = 'CLEAR_START'</t>
+  </si>
+  <si>
+    <t>清算后台账表校验@账务数量</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) from ACC_VOUCHER_DTAL WHERE EFFECTIVE_FLAG='Y' AND TRADE_DATE=20210319 AND TRADE_TYPE IN ('A4','A5')</t>
+  </si>
+  <si>
+    <t>COUNT(*):2</t>
+  </si>
+  <si>
+    <t>清算后台账表校验@A4账务</t>
+  </si>
+  <si>
+    <t>SELECT * from ACC_VOUCHER_DTAL WHERE EFFECTIVE_FLAG='Y' AND TRADE_DATE=20210319 AND TRADE_TYPE IN ('A4')</t>
+  </si>
+  <si>
+    <t>AMOUNT:110000.0
+STATUS:I</t>
+  </si>
+  <si>
+    <t>清算后台账表校验@A5账务</t>
+  </si>
+  <si>
+    <t>SELECT * from ACC_VOUCHER_DTAL WHERE EFFECTIVE_FLAG='Y' AND TRADE_DATE=20210319 AND TRADE_TYPE IN ('A5')</t>
+  </si>
+  <si>
+    <t>利息计提</t>
+  </si>
+  <si>
+    <t>echo "push CLRINTI.txt"
+cd mock_path
+rm *
+echo '{
+ "PRCCOD": "CLRINTI",
+ "WEBCOD": "",
+ "ERRMSG": "",
+ "ISUTIM": "",
+ "ISUDAT": "",
+ "RTNLVL": "",
+ "DALCOD": "",
+ "TARSVR": "",
+ "INFBDY": {
+     "CLRINTIY1":[{
+   "ztrxset":"INTI00000001"
+  }] 
+ },
+ "RTNCOD": "SUC0000"
+}' &gt; CLRINTI.txt
+cat CLRINTI.txt</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_INTEREST_ACCRUAL_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>利息计提后台账表校验@账务数量</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) from ACC_VOUCHER_DTAL WHERE EFFECTIVE_FLAG='Y' AND TRADE_TYPE IN ('L1','L3')</t>
+  </si>
+  <si>
+    <t>手续费计提</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_FEE_ACCRUAL_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>查询划扣至262信息</t>
+  </si>
+  <si>
+    <t>echo "push CLRBLQR.txt"
+cd mock_path
+rm *
+echo '{
+ "PRCCOD": "CLRBLQR",
+ "WEBCOD": "",
+ "ERRMSG": "",
+ "ISUTIM": "",
+ "ISUDAT": "",
+ "RTNLVL": "",
+ "DALCOD": "",
+ "TARSVR": "",
+ "INFBDY": {
+  "CLRBLQRY1":[{
+   "zavlbal":"1000000",
+   "zeacsts":"A"
+  }]
+ },
+ "RTNCOD": "SUC0000"
+}' &gt; CLRBLQR.txt
+cat CLRBLQR.txt</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_CUSTOMER_INFO_QY_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>"CUS_MARGIN_SCH":"110000"
+"CUSTOMER_NAME_CH":"小小测试007"
+"MARGIN_AMOUNT":110000
+"MARGIN_FLOAT_BALANCE":"1000"</t>
+  </si>
+  <si>
+    <t>LOCALSYS_ID
+ACCOUNT_NO
+MARGIN_NO
+MARGIN_NAME
+ACCOUNT_AMOUNT
+DELTA</t>
+  </si>
+  <si>
+    <t>划扣至262</t>
+  </si>
+  <si>
+    <t>echo "push CLRRTIN.txt"
+cd mock_path
+echo '{
+ "PRCCOD": "CLRRTIN",
+ "WEBCOD": "",
+ "ERRMSG": "",
+ "ISUTIM": "",
+ "ISUDAT": "",
+ "RTNLVL": "",
+ "DALCOD": "",
+ "TARSVR": "",
+ "INFBDY": {
+  "CLRRTINY1":[{
+   "ztrxset":"YYQX00000001"
+  }]
+ },
+ "RTNCOD": "SUC0000"
+}' &gt; CLRRTIN.txt
+cat CLRRTIN.txt</t>
+  </si>
+  <si>
+    <t>data={
+    "CUSTOMER_INFO":[
+        {
+            "MARGIN_LOAN_ID":"",
+            "FEE_LOAN_ID":"",
+            "LOCALSYS_ID":"${LOCALSYS_ID}",
+            "CUS_MARGIN_SCH":"110000",
+            "CUS_MARGIN_SCHED":"0",
+            "CUS_MARGIN_FLOAT":"11000",
+            "CUS_MARGIN_FLOATED":"0",
+            "CUS_SEET_SCHED":"0",
+            "CUS_SEET_SCH":"0",
+            "LOAN_AMOUNT":0,
+            "LOAN_FLAG":"0",
+            "CUSTOMER_NAME_CH":"小小测试007",
+            "MARGIN_AMOUNT":110000,
+            "FEE_AMOUNT":0,
+            "ACCOUNT_NO":"${ACCOUNT_NO}",
+            "MARGIN_NO":"${MARGIN_NO}",
+            "MARGIN_NAME":"${MARGIN_NAME}",
+            "ACCOUNT_AMOUNT":${ACCOUNT_AMOUNT},
+            "MARGIN_FLOAT_BALANCE":"1000",
+            "PAY_AMOUNT":0,
+            "DELTA":${DELTA},
+            "ADVANCE_FLAG":"1"
+        }
+    ],
+    "f":"IRS_TRANSFER_262_CNY",
+    "u":"143374",
+    "l":"${token}",
+    "e":"999"
+}</t>
+  </si>
+  <si>
+    <t>select * from CLEARING_PROCEDURE where TRADE_DATE = 20210319 and CLEAR_STEP = 'TRANSFER_262'</t>
+  </si>
+  <si>
+    <t>划至262后台账表校验</t>
+  </si>
+  <si>
+    <t>STATUS:S</t>
+  </si>
+  <si>
+    <t>划扣至上清所</t>
+  </si>
+  <si>
+    <t>echo "push CLROUTR.txt"
+cd mock_path
+echo '{
+ "PRCCOD": "CLROUTR",
+ "WEBCOD": "",
+ "ERRMSG": "",
+ "ISUTIM": "",
+ "ISUDAT": "",
+ "RTNLVL": "",
+ "DALCOD": "",
+ "TARSVR": "",
+ "INFBDY": {
+ },
+ "RTNCOD": "SUC0000"
+}' &gt; CLROUTR.txt
+cat CLROUTR.txt</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_TRANSFER_SCH_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>划至上清所后台账表校验</t>
+  </si>
+  <si>
+    <t>划至上清所后大额表检查</t>
+  </si>
+  <si>
+    <t>select * from ACC_AMOUNT_CONFIRM where ACCOUNT_TYPE='P1' AND send_status=0 and amount=110000</t>
+  </si>
+  <si>
+    <t>SEND_STATUS:0</t>
+  </si>
+  <si>
+    <t>大额回执查询</t>
+  </si>
+  <si>
+    <t>echo "push CLRTSQR.txt"
+cd mock_path
+echo '{
+ "PRCCOD": "CLRTSQR",
+ "WEBCOD": "",
+ "ERRMSG": "",
+ "ISUTIM": "",
+ "ISUDAT": "",
+ "RTNLVL": "",
+ "DALCOD": "",
+ "TARSVR": "",
+ "INFBDY": {
+  "CLRTSQRY1": [
+   {
+    "zrefnbr": "FX20191119001",
+    "ztrsamt": "10000",
+    "zstatus": "0",
+    "zeacnbr": "",
+    "zbalnbr": "" ,
+    "ztrxset": "INTI00000002"
+   }
+  ]
+ },
+ "RTNCOD": "SUC0000"
+}' &gt; CLRTSQR.txt
+cat CLRTSQR.txt</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_QUERY_RECEIPT_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>RECEIPT_RESULT:0</t>
+  </si>
+  <si>
+    <t>大额支付记录查询(大额模块)</t>
+  </si>
+  <si>
+    <t>data={
+    "PRODUCT": "*",
+    "PAY_ACCOUNT": "",
+    "PAY_NAME_CH": "",
+    "COLLECTION_ACCOUNT": "",
+    "COLLECTION_NAME_CH": "",
+    "TRADE_DATE": "",
+    "PAY_TYPE": "*",
+    "SEND_STATUS": "0",
+    "page_NO": 1,
+    "page_count": 10,
+    "tableDataID": "GETDATA_IRS_LargePaymentConfirm",
+    "f": "FRAM_GetTableDataList",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>ID
+PAY_ACCOUNT
+PAY_NAME_CH
+COLLECTION_ACCOUNT
+COLLECTION_NAME_CH
+DIGEST
+PRIMARY_KEY
+ACC_MAIN_REF
+RN</t>
+  </si>
+  <si>
+    <t>大额支付确认(大额模块)</t>
+  </si>
+  <si>
+    <t>echo "push CLRINTI.txt"
+cd mock_path
+echo '{
+ "PRCCOD": "CLRINTI",
+ "WEBCOD": "",
+ "ERRMSG": "",
+ "ISUTIM": "",
+ "ISUDAT": "",
+ "RTNLVL": "",
+ "DALCOD": "",
+ "TARSVR": "",
+ "INFBDY": {
+     "CLRINTIY1":[{
+   "ztrxset":"INTI00000001"
+  }] 
+ },
+ "RTNCOD": "SUC0000"
+}' &gt; CLRINTI.txt
+cat CLRINTI.txt</t>
+  </si>
+  <si>
+    <t>data={
+    "ID": "${ID}",
+    "PRODUCT": "IRS",
+    "TRADE_DATE": "2021-03-19",
+    "PAY_ACCOUNT": "${PAY_ACCOUNT}",
+    "PAY_NAME_CH": "${PAY_NAME_CH}",
+    "COLLECTION_ACCOUNT": "${COLLECTION_ACCOUNT}",
+    "COLLECTION_NAME_CH": "${COLLECTION_NAME_CH}",
+    "ACCOUNT_TYPE": "P1",
+    "AMOUNT": "110000",
+    "SEND_STATUS": "0",
+    "DIGEST": "${DIGEST}",
+    "HANDWORK_FLAG": "0",
+    "CREATE_TIME": "",
+    "FAIL_REASON": "",
+    "PRIMARY_KEY": "${PRIMARY_KEY}",
+    "ZTRXSET": "",
+    "MODIFY_TIME": "",
+    "ACC_MAIN_REF": "${ACC_MAIN_REF}",
+    "CURRENCY": "CNY",
+    "RN": "1",
+    "f": "IRS_AMOUNT_CONFIRM",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>select * from ACC_AMOUNT_CONFIRM where ACCOUNT_TYPE='P1' and amount=110000</t>
+  </si>
+  <si>
+    <t>SEND_STATUS:1</t>
+  </si>
+  <si>
+    <t>确认上清所入账（清算模块）</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_CONFIRM_SCH_CREDIT_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>select * from ACC_VOUCHER_DTAL where TRADE_TYPE='P1' and amount=110000</t>
+  </si>
+  <si>
+    <t>释放保证金上浮</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_RELEASE_MARGIN_CNY",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>"CLEARING_LOG":["释放保证金上浮开始...","当前日期，客户不需要释放上浮保证金！！"]</t>
+  </si>
+  <si>
+    <t>切日</t>
+  </si>
+  <si>
+    <t>data={
+    "f": "IRS_CLEAR_CUT_DATE",
+    "u": "143374",
+    "l": "${token}",
+    "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>SELECT PARAM_VALUE FROM BASE_PARAM WHERE ID='TRADE_DATE'</t>
+  </si>
+  <si>
+    <t>PARAM_VALUE:20210320</t>
+  </si>
+  <si>
+    <t>系统日期修改</t>
+  </si>
+  <si>
+    <t>date -s "2021-03-21 09:29:59"</t>
+  </si>
+  <si>
+    <t>切日后客户保证金余额检验</t>
+  </si>
+  <si>
+    <t>data={
+ "PRODUCT": "IRS",
+ "CUSTOMER_ID": "",
+ "ACCOUNT_NO": "",
+ "MARGIN_NO": "",
+ "CUSTOMER_NAME_CH": "",
+ "LOCALSYS_ID": "${LOCALSYS_ID_07}",
+ "page_count": 10,
+ "page_NO": 1,
+ "tableDataID": "GETDATA_IRS_RISKQUOTAMANAGE",
+ "f": "FRAM_GetTableDataList",
+ "u": "174729",
+ "l": "63D3042433D343D314D3B3B3C3B333B3532453C3ef6d2a398ae22646e314092d982a03c0",
+ "e": "999"
+}</t>
+  </si>
+  <si>
+    <t>"LOW_MARGIN_RQ":"120000"
+"LOW_MARGIN_RQFLOAT":"12000"
+"TDLOW_MARGIN_RQ":"120000"
+"TDLOW_MARGIN_RQFLOAT":"1000"</t>
   </si>
 </sst>
 </file>
@@ -147,12 +1190,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -206,45 +1255,114 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -558,7 +1676,7 @@
   <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" style="24" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="27.44140625" customWidth="1"/>
     <col min="4" max="6" width="10.44140625" customWidth="1"/>
@@ -569,140 +1687,1653 @@
     <col min="11" max="11" width="52.6640625" customWidth="1"/>
     <col min="12" max="12" width="43.33203125" customWidth="1"/>
     <col min="13" max="15" width="26.44140625" customWidth="1"/>
-    <col min="16" max="16" width="26.44140625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="26.44140625" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="27" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:16" s="22" customFormat="1" ht="27" customHeight="1">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" ht="28.8">
-      <c r="A2" s="9">
+    <row r="2" spans="1:16" s="23" customFormat="1" ht="72">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="29">
         <v>111</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="6" t="s">
+      <c r="E2" s="29"/>
+      <c r="F2" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="H2" s="25">
+        <v>9192</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="J2" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7" t="s">
+      <c r="K2" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="L2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="M2" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="N2" s="29" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" ht="28.8">
-      <c r="A3" s="9">
+      <c r="O2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="23" customFormat="1" ht="72">
+      <c r="A3" s="28">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="29">
         <v>111</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="6" t="s">
+      <c r="E3" s="29"/>
+      <c r="F3" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="H3" s="25">
+        <v>9192</v>
+      </c>
+      <c r="I3" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="J3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6" t="s">
+      <c r="K3" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>28</v>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="47.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="3" customWidth="1"/>
+    <col min="11" max="12" width="20" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="32.77734375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="29.33203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.21875" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="27" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="11"/>
+    </row>
+    <row r="3" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A3" s="34"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="11"/>
+    </row>
+    <row r="4" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A4" s="34"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A5" s="34"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A6" s="34"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A7" s="34"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A8" s="34"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A9" s="34"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A12" s="34"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A14" s="34"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A15" s="34"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A16" s="34"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A17" s="34"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A18" s="34"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A19" s="34"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A20" s="34"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A21" s="34"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="2" customFormat="1" ht="16.95" customHeight="1">
+      <c r="A22" s="35"/>
+      <c r="B22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q22" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="2" customFormat="1" ht="18" customHeight="1">
+      <c r="A23" s="35"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q23" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="2" customFormat="1" ht="18" customHeight="1">
+      <c r="A24" s="35"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q24" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A25" s="34"/>
+      <c r="B25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A26" s="34"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A27" s="34"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A28" s="34"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q28" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A29" s="34"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A30" s="34"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="11"/>
+    </row>
+    <row r="31" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A31" s="34"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q31" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A32" s="34"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="11"/>
+    </row>
+    <row r="33" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A33" s="34"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="O33" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="11"/>
+    </row>
+    <row r="34" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A34" s="34"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q34" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A35" s="34"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q35" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A36" s="34"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="11"/>
+    </row>
+    <row r="37" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A37" s="34"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q37" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A38" s="34"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q38" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A39" s="34"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q39" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A40" s="34"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="N40" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="11"/>
+    </row>
+    <row r="41" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A41" s="34"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q41" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A42" s="34"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q42" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A43" s="34"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="O43" s="11"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="11"/>
+    </row>
+    <row r="44" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A44" s="34"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q44" s="15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="22.05" customHeight="1">
+      <c r="A45" s="34"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O45" s="11"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="11"/>
+    </row>
+    <row r="46" spans="1:17" s="1" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A46" s="34"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N46" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="O46" s="15"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>